--- a/MiniTemplate/Datas/treasure.xlsx
+++ b/MiniTemplate/Datas/treasure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F744429-8D46-4C65-966D-1C3EA40B2581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5452B2-241F-407D-8B89-EFA42305D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,10 +680,10 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1"/>
     </row>

--- a/MiniTemplate/Datas/treasure.xlsx
+++ b/MiniTemplate/Datas/treasure.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5452B2-241F-407D-8B89-EFA42305D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -42,6 +38,18 @@
     <t>name</t>
   </si>
   <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>minNum</t>
+  </si>
+  <si>
+    <t>maxNum</t>
+  </si>
+  <si>
+    <t>globalDefine</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -61,102 +69,76 @@
   </si>
   <si>
     <t>宝藏ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝藏名称</t>
+  </si>
+  <si>
+    <t>宝藏物品 (id, num, weight)</t>
+  </si>
+  <si>
+    <t>最小宝藏数</t>
+  </si>
+  <si>
+    <t>最大宝藏数</t>
+  </si>
+  <si>
+    <t>对应宝箱名</t>
   </si>
   <si>
     <t>普通宝箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,1000|1000,1,1000|1003,1,1000|1006,1,1000|1009,1,1000|3000,1,500|10000,1,100</t>
+  </si>
+  <si>
+    <t>FeiCuiLinHaiTreasure1</t>
   </si>
   <si>
     <t>木质宝箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1,1000</t>
   </si>
   <si>
     <t>银质宝箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2,1000|10000,1,1000|1001,1,1000</t>
+  </si>
+  <si>
+    <t>FeiCuiLinHaiTreasure2</t>
   </si>
   <si>
     <t>金质宝箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1,1000|1005,1,1000|1008,1,1000</t>
   </si>
   <si>
     <t>翡翠之箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,1,1000</t>
   </si>
   <si>
     <t>传说翡翠之箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝藏名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>content</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c,s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝藏物品 (id, num, weight)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1,1000|1000,1,1000|1003,1,1000|1006,1,1000|1009,1,1000|3000,1,500|10000,1,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,2,1000|10000,1,1000|1001,1,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1,1000|1005,1,1000|1008,1,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,1,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10002,1,1000|10001,2,1000|10002,4,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>minNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最小宝藏数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大宝藏数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,29 +147,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -195,9 +500,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -205,27 +752,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -483,26 +1074,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="87.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
+    <col min="3" max="3" width="13.4416666666667" customWidth="1"/>
+    <col min="4" max="4" width="87.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
-    <col min="8" max="8" width="43.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
+    <col min="8" max="8" width="43.5583333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.44166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,85 +1103,97 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="G4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>1000</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -598,16 +1201,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1001</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -616,32 +1222,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>1002</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>1003</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>24</v>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -649,17 +1258,17 @@
       <c r="F8">
         <v>3</v>
       </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>1004</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -667,17 +1276,17 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10">
         <v>1005</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -685,85 +1294,85 @@
       <c r="F10">
         <v>15</v>
       </c>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="1"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="1"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D26" s="1"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="G29" s="1"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="D11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="D12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="D13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="D14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="D15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="D16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="4:7">
+      <c r="D17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="4:7">
+      <c r="D18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="4:7">
+      <c r="D19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="4:7">
+      <c r="D20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="4:7">
+      <c r="D21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="4:7">
+      <c r="D22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="4:7">
+      <c r="D23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="4:7">
+      <c r="D24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="4:7">
+      <c r="D25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="4:7">
+      <c r="D26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="4:7">
+      <c r="D27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="4:7">
+      <c r="D28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="4:7">
+      <c r="G29" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/treasure.xlsx
+++ b/MiniTemplate/Datas/treasure.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="28785" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -86,22 +86,22 @@
     <t>对应宝箱名</t>
   </si>
   <si>
-    <t>普通宝箱</t>
-  </si>
-  <si>
-    <t>2,1,1000|1000,1,1000|1003,1,1000|1006,1,1000|1009,1,1000|3000,1,500|10000,1,100</t>
+    <t>[翡翠林海]普通宝箱</t>
+  </si>
+  <si>
+    <t>1000,1,1000|1003,1,1000|1006,1,1000|1009,1,1000|3000,1,500|10000,1,100</t>
   </si>
   <si>
     <t>FeiCuiLinHaiTreasure1</t>
   </si>
   <si>
-    <t>木质宝箱</t>
-  </si>
-  <si>
-    <t>3,1,1000</t>
-  </si>
-  <si>
-    <t>银质宝箱</t>
+    <t>[翡翠林海]木质宝箱</t>
+  </si>
+  <si>
+    <t>2,1,500|1000,2,1000|1003,2,1000|1006,2,1000|1009,2,1000|3000,1,1000|10000,1,200</t>
+  </si>
+  <si>
+    <t>[翡翠林海]银质宝箱</t>
   </si>
   <si>
     <t>3,2,1000|10000,1,1000|1001,1,1000</t>
@@ -110,19 +110,19 @@
     <t>FeiCuiLinHaiTreasure2</t>
   </si>
   <si>
-    <t>金质宝箱</t>
+    <t>[翡翠林海]金质宝箱</t>
   </si>
   <si>
     <t>1002,1,1000|1005,1,1000|1008,1,1000</t>
   </si>
   <si>
-    <t>翡翠之箱</t>
+    <t>[翡翠林海]翡翠之箱</t>
   </si>
   <si>
     <t>10001,1,1000</t>
   </si>
   <si>
-    <t>传说翡翠之箱</t>
+    <t>[翡翠林海]传说翡翠之箱</t>
   </si>
   <si>
     <t>10002,1,1000|10001,2,1000|10002,4,1000</t>
@@ -138,14 +138,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -618,133 +611,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -752,10 +745,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1084,7 +1077,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
-    <col min="3" max="3" width="13.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
     <col min="4" max="4" width="87.6666666666667" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -1221,6 +1214,9 @@
       <c r="F6">
         <v>1</v>
       </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7">

--- a/MiniTemplate/Datas/treasure.xlsx
+++ b/MiniTemplate/Datas/treasure.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5DE85B-2005-42A9-989A-27DEADC4B6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28785" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -93,7 +89,7 @@
     <t>[翡翠林海]普通宝箱</t>
   </si>
   <si>
-    <t>1000,1,1000|1003,1,1000|1006,1,1000|1009,1,1000|3000,1,500|10000,1,100</t>
+    <t>1000,1,20|1000,2,10|1003,1,20|1003,2,10|1006,1,20|1006,2,10|1009,1,4|3000,1,5|10000,1,1|2,1,5</t>
   </si>
   <si>
     <t>FeiCuiLinHaiTreasure1</t>
@@ -102,58 +98,56 @@
     <t>[翡翠林海]木质宝箱</t>
   </si>
   <si>
-    <t>2,1,500|1000,2,1000|1003,2,1000|1006,2,1000|1009,2,1000|3000,1,1000|10000,1,200</t>
+    <t>1000,2,20|1001,1,5|1003,2,20|1004,1,5|1006,2,20|1007,1,5|1009,1,5|3000,1,10|10000,1,1|2,1,10</t>
   </si>
   <si>
     <t>[翡翠林海]银质宝箱</t>
   </si>
   <si>
+    <t>1000,2,1000|1001,1,500|1003,2,1000|1004,1,500|1006,2,1000|1007,1,500|1009,1,100|1010,1,50|10000,1,100|10000,2,100|10001,1,50|2,1,500|3,1,50</t>
+  </si>
+  <si>
+    <t>FeiCuiLinHaiTreasure2</t>
+  </si>
+  <si>
     <t>[翡翠林海]金质宝箱</t>
   </si>
   <si>
+    <t>1001,2,1000|1002,1,500|1004,2,1000|1005,1,500|1007,2,1000|1008,1,500|1010,1,500|10000,1,1000|10001,1,100|2,1,1000|3,1,500</t>
+  </si>
+  <si>
+    <t>FeiCuiLinHaiTreasure3</t>
+  </si>
+  <si>
     <t>[翡翠林海]翡翠之箱</t>
   </si>
   <si>
+    <t>1002,1,1000|1005,1,1000|1008,1,1000|1010,1,1000|1011,1,10|10000,1,1000|10001,1,500|10002,1,100</t>
+  </si>
+  <si>
+    <t>FeiCuiLinHaiTreasure4</t>
+  </si>
+  <si>
     <t>[翡翠林海]传说翡翠之箱</t>
   </si>
   <si>
-    <t>2,2,1000|3,1,800|1001,1,200|1004,1,200|1007,1,200|1010,1,200|3000,3,1000|10000,1,400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3,1000|3,1,1000|1002,1,100|1005,1,100|1008,1,100|1011,1,100|10001,1,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,2,1000|4,1,100|1002,1,500|1005,2,500|1008,2,500|1011,2,500|10001,1,500|10002,1,200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,1,200|1002,1,1000|1005,1,1000|1008,1,1000|1011,1,1000|10001,2,1000|10002,1,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeiCuiLinHaiTreasure2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeiCuiLinHaiTreasure3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeiCuiLinHaiTreasure4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>1002,1,100|1005,1,100|1008,1,100|1010,1,100|1011,1,100|10002,1,100</t>
   </si>
   <si>
     <t>FeiCuiLinHaiTreasure5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,29 +156,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -192,9 +509,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -202,27 +761,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -480,18 +1083,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="7.125" customWidth="1"/>
     <col min="3" max="3" width="22.75" customWidth="1"/>
-    <col min="4" max="4" width="87.625" customWidth="1"/>
+    <col min="4" max="4" width="143" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="25.75" customWidth="1"/>
@@ -499,7 +1102,7 @@
     <col min="9" max="9" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +1125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -545,7 +1148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -568,7 +1171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -591,7 +1194,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -605,13 +1208,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -622,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -631,15 +1234,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -647,147 +1250,147 @@
       <c r="F7">
         <v>3</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3" t="s">
         <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D24" s="1"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D25" s="1"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D26" s="1"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="G29" s="1"/>
+    <row r="11" spans="1:7">
+      <c r="D11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="D12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="D13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="D14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="D15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="D16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="4:7">
+      <c r="D17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="4:7">
+      <c r="D18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="4:7">
+      <c r="D19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="4:7">
+      <c r="D20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="4:7">
+      <c r="D21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="4:7">
+      <c r="D22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="4:7">
+      <c r="D23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="4:7">
+      <c r="D24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="4:7">
+      <c r="D25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="4:7">
+      <c r="D26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="4:7">
+      <c r="D27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="4:7">
+      <c r="D28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="4:7">
+      <c r="G29" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>